--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N98_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N98_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.72174128023486</v>
+        <v>3.692282958038165</v>
       </c>
       <c r="D2" t="n">
-        <v>26.21521493572368</v>
+        <v>4.259972427055097</v>
       </c>
       <c r="E2" t="n">
-        <v>4.274433660798815</v>
+        <v>0.6945954698798074</v>
       </c>
       <c r="F2" t="n">
-        <v>5.371605701134751</v>
+        <v>0.872885926434397</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.11116217311635</v>
+        <v>2.455563853131407</v>
       </c>
       <c r="D3" t="n">
-        <v>17.10016334482665</v>
+        <v>2.778776543534331</v>
       </c>
       <c r="E3" t="n">
-        <v>4.274433660798815</v>
+        <v>0.6945954698798074</v>
       </c>
       <c r="F3" t="n">
-        <v>5.371605701134751</v>
+        <v>0.872885926434397</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.14363714894169</v>
+        <v>4.085841036703024</v>
       </c>
       <c r="D4" t="n">
-        <v>13.43999232124191</v>
+        <v>2.18399875220181</v>
       </c>
       <c r="E4" t="n">
-        <v>4.274433660798815</v>
+        <v>0.6945954698798074</v>
       </c>
       <c r="F4" t="n">
-        <v>5.371605701134751</v>
+        <v>0.872885926434397</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
